--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>18/07 17:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>14/07 19:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>17/07 02:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>19/07 21:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>50</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>40</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>19/07 15:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>15/07 00:15</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>20/07 10:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>55</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>18/07 23:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/07 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>11</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/07 18:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>40</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>17/07 17:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>40</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45852.08298301977</v>
+        <v>45852.08298302083</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Kamil Majc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kamil Majchrzak – Terence AtmaneATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>14/07 08:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+45,8%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45852.1567258888</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Slavia Pra</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Slavia Prague – FC Hradec KraloveSynot League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20/07 18:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+27,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45852.1567258888</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Central Co</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Central Cordoba – Cerro Largo FCCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>15/07 22:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45852.1567258888</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Estudiante</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21/07 22:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45852.1567258888</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>14/07 08:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45852.1567258888</v>
+        <v>45852.1567258912</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>20/07 18:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>60</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45852.1567258888</v>
+        <v>45852.1567258912</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>15/07 22:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45852.1567258888</v>
+        <v>45852.1567258912</v>
       </c>
     </row>
     <row r="30">
@@ -1715,23 +1709,66 @@
           <t>21/07 22:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>45</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45852.1567258912</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Instituto </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Instituto AC Cordoba – River PlateLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20/07 00:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+8,77%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45852.1567258888</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+6,43%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45852.19711664528</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -1752,10 +1752,8 @@
           <t>20/07 00:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45852.19711664528</v>
+        <v>45852.19711664352</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,51 @@
         <v>45852.19711664352</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 5.5 | Deportivo </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>14/07 19:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+6,92%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45852.27538855411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>14/07 19:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,52 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45852.27538855411</v>
+        <v>45852.27538855324</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | H 1 (−1.5) | Rejchtman </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Rejchtman Vinciguerra, William – Jesper De JongATP 250 Bastad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>14/07 11:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+41,1%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45852.31000474748</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -1838,10 +1838,8 @@
           <t>14/07 11:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>75</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45852.31000474748</v>
+        <v>45852.31000474537</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,186 @@
         <v>45852.31000474537</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | T.Wurth – </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>T.Wurth – D.ParryWTA - Hambourg F</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>14/07 11:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45852.39661662476</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dinamo Buc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dinamo Bucarest – FC BotosaniLiga 1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>21/07 18:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45852.39661662476</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Viborg FF </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Viborg FF – FC CopenhagueSuperLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>18/07 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45852.39661662476</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Deportes T</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Deportes Tolima – Santa FePrimera A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/07 01:10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+3,55%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45852.39661662476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>14/07 11:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45852.39661662476</v>
+        <v>45852.39661662037</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>45</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45852.39661662476</v>
+        <v>45852.39661662037</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>18/07 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>50</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45852.39661662476</v>
+        <v>45852.39661662037</v>
       </c>
     </row>
     <row r="37">
@@ -2016,23 +2010,111 @@
           <t>19/07 01:10</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>45</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+3,55%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45852.39661662037</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Aleksandar</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Aleksandar Vukic – Emilio NavaATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>15/07 02:10</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+9,45%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45852.43494956407</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FK Shkendi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FK Shkendija – The New SaintsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15/07 18:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2,30%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>+3,55%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>45852.39661662476</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+4,78%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45852.43494956407</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>15/07 02:10</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45852.43494956407</v>
+        <v>45852.43494956019</v>
       </c>
     </row>
     <row r="39">
@@ -2098,23 +2096,66 @@
           <t>15/07 18:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>45</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+4,78%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45852.43494956019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico T</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/07 00:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>+4,78%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>45852.43494956407</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+5,20%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45852.47255354392</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>19/07 00:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,52 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45852.47255354392</v>
+        <v>45852.47255354167</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>15/07 02:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+3,61%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45852.53403638409</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>15/07 02:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>25</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,52 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45852.53403638409</v>
+        <v>45852.53403638889</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21re période | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – VirtusEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21re période</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15/07 19:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+4,03%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45852.56810667701</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>15/07 19:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>27.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>27</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,52 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45852.56810667701</v>
+        <v>45852.56810667824</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Viktoria P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen – Servette FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+1,33%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45852.60023971047</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
+      <c r="F43" t="n">
+        <v>1.21</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,97 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45852.60023971047</v>
+        <v>45852.60023971065</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set2e participant | Taro Danie</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Taro Daniel – Hernandez Serrano, Juan AlejandroATP 250 Los Cabos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>15/07 04:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+2,82%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45852.64305780809</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball | Plus que 3.5 | Chine – Fr</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chine – FranceMonde - Ligue des Nations H</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16/07 11:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+1,12%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45852.64305780809</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -2311,10 +2311,8 @@
           <t>15/07 04:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.7</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45852.64305780809</v>
+        <v>45852.6430578125</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>16/07 11:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45852.64305780809</v>
+        <v>45852.6430578125</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +2371,51 @@
         <v>45852.6430578125</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui | Arthur Rin</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech – Francesco PassaroATP 250 Gstaad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15/07 09:40</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+1,89%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45852.72361547661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -2397,10 +2397,8 @@
           <t>15/07 09:40</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.15</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45852.72361547661</v>
+        <v>45852.72361547454</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,96 @@
         <v>45852.72361547454</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico L</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atletico Lanus – Rosario CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/07 19:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+14,8%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45852.85175156825</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Martin</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/07 13:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+5,82%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45852.85175156825</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>50</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45852.85175156825</v>
+        <v>45852.8517515625</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45852.85175156825</v>
+        <v>45852.8517515625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Ilves –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FC Ilves – Shakhtar DonetskLigue Europa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/07 16:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+2,54%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45852.89075763585</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>40</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,52 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45852.89075763585</v>
+        <v>45852.89075763889</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Newell's O</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys – CA BanfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20/07 19:45</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+8,01%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45852.93214711377</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-14.xlsx
+++ b/data/valuebets_database_2025-07-14.xlsx
@@ -2569,10 +2569,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45852.93214711377</v>
+        <v>45852.93214711805</v>
       </c>
     </row>
   </sheetData>
